--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.77779505490122</v>
+        <v>5.001391696421448</v>
       </c>
       <c r="D2" t="n">
-        <v>30.90441982682273</v>
+        <v>5.021968221858693</v>
       </c>
       <c r="E2" t="n">
-        <v>5.392764609321031</v>
+        <v>0.8763242490146674</v>
       </c>
       <c r="F2" t="n">
-        <v>5.466995857590902</v>
+        <v>0.8883868268585214</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.00601677635745</v>
+        <v>3.413477726158086</v>
       </c>
       <c r="D3" t="n">
-        <v>21.12494977641265</v>
+        <v>3.432804338667055</v>
       </c>
       <c r="E3" t="n">
-        <v>5.392764609321031</v>
+        <v>0.8763242490146674</v>
       </c>
       <c r="F3" t="n">
-        <v>5.466995857590902</v>
+        <v>0.8883868268585214</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.92967595786463</v>
+        <v>4.213572343153002</v>
       </c>
       <c r="D4" t="n">
-        <v>25.79056629910007</v>
+        <v>4.190967023603761</v>
       </c>
       <c r="E4" t="n">
-        <v>5.392764609321031</v>
+        <v>0.8763242490146674</v>
       </c>
       <c r="F4" t="n">
-        <v>5.466995857590902</v>
+        <v>0.8883868268585214</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.61761814553212</v>
+        <v>2.37536294864897</v>
       </c>
       <c r="D5" t="n">
-        <v>14.4193964322959</v>
+        <v>2.343151920248084</v>
       </c>
       <c r="E5" t="n">
-        <v>5.392764609321031</v>
+        <v>0.8763242490146674</v>
       </c>
       <c r="F5" t="n">
-        <v>5.466995857590902</v>
+        <v>0.8883868268585214</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.71049215996529</v>
+        <v>4.015454975994359</v>
       </c>
       <c r="D6" t="n">
-        <v>24.65860391259479</v>
+        <v>4.007023135796654</v>
       </c>
       <c r="E6" t="n">
-        <v>5.392764609321031</v>
+        <v>0.8763242490146674</v>
       </c>
       <c r="F6" t="n">
-        <v>5.466995857590902</v>
+        <v>0.8883868268585214</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
